--- a/output/IMG_9691.xlsx
+++ b/output/IMG_9691.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="得意先別／営業目標" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -579,7 +579,11 @@
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>得意先別／営業目標</t>
+        </is>
+      </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="2" t="n"/>

--- a/output/IMG_9691.xlsx
+++ b/output/IMG_9691.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>26,366,877</t>
+          <t>28,366,877</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>9,318,528</t>
+          <t>9,318,522</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>6,008,094</t>
+          <t>6,608,094</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">

--- a/output/IMG_9691.xlsx
+++ b/output/IMG_9691.xlsx
@@ -3160,7 +3160,7 @@
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>6,608,094</t>
+          <t>6,008,094</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr">

--- a/output/IMG_9691.xlsx
+++ b/output/IMG_9691.xlsx
@@ -3165,7 +3165,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>8,984,250</t>
+          <t>9,984,250</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr">

--- a/output/IMG_9691.xlsx
+++ b/output/IMG_9691.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="得意先別／営業目標" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="（株）ジュン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,30 +28,38 @@
     <font>
       <b val="1"/>
       <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <sz val="8"/>
+      <sz val="10"/>
     </font>
     <font>
       <color rgb="00000000"/>
-      <sz val="8"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+        <bgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -61,140 +69,39 @@
     </border>
     <border>
       <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom style="medium"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium"/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="medium"/>
-    </border>
-    <border>
-      <left style="medium"/>
       <right style="thin"/>
-      <top style="medium"/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="medium"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="medium"/>
       <top style="thin"/>
       <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="medium"/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="medium"/>
-    </border>
-    <border>
-      <left style="medium"/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="medium"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -561,3376 +468,3397 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L62"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14" customHeight="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>得意先別／営業目標</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+          <t>（株）ジュン</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>得意先別／営業目標　　営業１課　　大久保・関谷・金柿</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>S50</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>月別</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>前々年度当月</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>前年度当月</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>本年度当月</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>本年度目標</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>達成%</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>前々年度累計</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>前年度累計</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>本年度累計</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>目標値累計</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>達成%</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="14" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>4月</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>売上額</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>23,210,056</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>24,184,652</t>
         </is>
       </c>
-      <c r="E3" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>29,408,606</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>25,890,000</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>113.5</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>23,210,056</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr">
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>24,184,652</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>29,408,606</t>
         </is>
       </c>
-      <c r="K3" s="7" t="inlineStr">
+      <c r="K6" s="6" t="inlineStr">
         <is>
           <t>25,890,000</t>
         </is>
       </c>
-      <c r="L3" s="7" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>113.5</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="14" customHeight="1">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="9" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>粗利額</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>6,743,249</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>9,759,531</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>10,272,580</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>9,408,070</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>109.1</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>6,743,249</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>9,759,531</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>10,272,580</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>9,408,070</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L7" s="7" t="inlineStr">
         <is>
           <t>109.1</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="14" customHeight="1">
-      <c r="A5" s="8" t="n"/>
-      <c r="B5" s="9" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>粗利%</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>29.1</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>40.4</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>34.9</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>29.1</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>40.4</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>34.9</t>
         </is>
       </c>
-      <c r="K5" s="11" t="inlineStr">
+      <c r="K8" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="L5" s="11" t="n"/>
-    </row>
-    <row r="6" ht="14" customHeight="1">
-      <c r="A6" s="12" t="n"/>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="L8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>在庫額</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>48,074,189</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>29,924,156</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>28,078,678</t>
         </is>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>48,074,189</t>
         </is>
       </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>29,924,156</t>
         </is>
       </c>
-      <c r="J6" s="15" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>28,078,678</t>
         </is>
       </c>
-      <c r="K6" s="15" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="L6" s="15" t="n"/>
-    </row>
-    <row r="7" ht="14" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="L9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>5月</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>売上額</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>29,854,020</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>23,617,340</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>28,366,877</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>29,210,000</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>90.2</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>53,064,076</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>47,801,992</t>
         </is>
       </c>
-      <c r="J7" s="7" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>55,775,483</t>
         </is>
       </c>
-      <c r="K7" s="7" t="inlineStr">
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>55,100,000</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>101.2</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="14" customHeight="1">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="9" t="inlineStr">
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>粗利額</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>10,352,989</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>5,411,399</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>9,533,734</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>10,613,230</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G11" s="7" t="inlineStr">
         <is>
           <t>89.8</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>17,096,238</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>15,170,930</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>19,806,314</t>
         </is>
       </c>
-      <c r="K8" s="11" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>20,021,300</t>
         </is>
       </c>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="L11" s="7" t="inlineStr">
         <is>
           <t>98.9</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="14" customHeight="1">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="9" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>粗利%</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>34.7</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>22.9</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>36.2</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>32.2</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>31.7</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>35.5</t>
         </is>
       </c>
-      <c r="K9" s="11" t="inlineStr">
+      <c r="K12" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="L9" s="11" t="n"/>
-    </row>
-    <row r="10" ht="14" customHeight="1">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="L12" s="7" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>在庫額</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>40,887,701</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>31,654,636</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>27,007,459</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="inlineStr">
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>40,887,701</t>
         </is>
       </c>
-      <c r="I10" s="15" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>31,654,636</t>
         </is>
       </c>
-      <c r="J10" s="15" t="inlineStr">
+      <c r="J13" s="7" t="inlineStr">
         <is>
           <t>27,007,459</t>
         </is>
       </c>
-      <c r="K10" s="15" t="inlineStr">
+      <c r="K13" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="L10" s="15" t="n"/>
-    </row>
-    <row r="11" ht="14" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="L13" s="7" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>6月</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>売上額</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>30,824,892</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>28,120,227</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>30,184,029</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>32,200,000</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>93.7</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>83,888,968</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>75,922,219</t>
         </is>
       </c>
-      <c r="J11" s="7" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>85,959,512</t>
         </is>
       </c>
-      <c r="K11" s="7" t="inlineStr">
+      <c r="K14" s="6" t="inlineStr">
         <is>
           <t>87,300,000</t>
         </is>
       </c>
-      <c r="L11" s="7" t="inlineStr">
+      <c r="L14" s="6" t="inlineStr">
         <is>
           <t>98.4</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="14" customHeight="1">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="9" t="inlineStr">
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>粗利額</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>10,455,433</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>8,883,694</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>10,729,326</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>11,698,600</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G15" s="7" t="inlineStr">
         <is>
           <t>91.7</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>27,551,671</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>24,054,624</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
+      <c r="J15" s="7" t="inlineStr">
         <is>
           <t>30,535,640</t>
         </is>
       </c>
-      <c r="K12" s="11" t="inlineStr">
+      <c r="K15" s="7" t="inlineStr">
         <is>
           <t>31,719,900</t>
         </is>
       </c>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>96.2</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="14" customHeight="1">
-      <c r="A13" s="8" t="n"/>
-      <c r="B13" s="9" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>粗利%</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>33.9</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>35.5</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>32.8</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>35.5</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="K16" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="L13" s="11" t="n"/>
-    </row>
-    <row r="14" ht="14" customHeight="1">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="L16" s="7" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>在庫額</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>37,307,954</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>31,610,441</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>29,903,836</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="G14" s="15" t="n"/>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>37,307,954</t>
         </is>
       </c>
-      <c r="I14" s="15" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>31,610,441</t>
         </is>
       </c>
-      <c r="J14" s="15" t="inlineStr">
+      <c r="J17" s="7" t="inlineStr">
         <is>
           <t>29,903,836</t>
         </is>
       </c>
-      <c r="K14" s="15" t="inlineStr">
+      <c r="K17" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="L14" s="15" t="n"/>
-    </row>
-    <row r="15" ht="14" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="L17" s="7" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>7月</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>売上額</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>28,982,498</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>30,982,498</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>31,499,403</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>30,112,906</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>33,040,000</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>91.1</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>112,871,466</t>
         </is>
       </c>
-      <c r="I15" s="7" t="inlineStr">
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>107,421,622</t>
         </is>
       </c>
-      <c r="J15" s="7" t="inlineStr">
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>116,072,418</t>
         </is>
       </c>
-      <c r="K15" s="7" t="inlineStr">
+      <c r="K18" s="6" t="inlineStr">
         <is>
           <t>120,340,000</t>
         </is>
       </c>
-      <c r="L15" s="7" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
         <is>
           <t>96.4</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="14" customHeight="1">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="9" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>粗利額</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>8,749,970</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>10,580,901</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>10,558,533</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>12,003,520</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>87.9</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>36,301,641</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>34,635,525</t>
         </is>
       </c>
-      <c r="J16" s="11" t="inlineStr">
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>41,094,173</t>
         </is>
       </c>
-      <c r="K16" s="11" t="inlineStr">
+      <c r="K19" s="7" t="inlineStr">
         <is>
           <t>43,723,420</t>
         </is>
       </c>
-      <c r="L16" s="11" t="inlineStr">
+      <c r="L19" s="7" t="inlineStr">
         <is>
           <t>93.9</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="14" customHeight="1">
-      <c r="A17" s="8" t="n"/>
-      <c r="B17" s="9" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>粗利%</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>30.2</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>33.6</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>35.1</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>32.1</t>
         </is>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>32.2</t>
         </is>
       </c>
-      <c r="J17" s="11" t="inlineStr">
+      <c r="J20" s="7" t="inlineStr">
         <is>
           <t>35.4</t>
         </is>
       </c>
-      <c r="K17" s="11" t="inlineStr">
+      <c r="K20" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="L17" s="11" t="n"/>
-    </row>
-    <row r="18" ht="14" customHeight="1">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="L20" s="7" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>在庫額</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>46,221,370</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>31,364,888</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>28,837,114</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="G18" s="15" t="n"/>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>46,221,370</t>
         </is>
       </c>
-      <c r="I18" s="15" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>31,364,888</t>
         </is>
       </c>
-      <c r="J18" s="15" t="inlineStr">
+      <c r="J21" s="7" t="inlineStr">
         <is>
           <t>28,837,114</t>
         </is>
       </c>
-      <c r="K18" s="15" t="inlineStr">
+      <c r="K21" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="L18" s="15" t="n"/>
-    </row>
-    <row r="19" ht="14" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="L21" s="7" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>売上額</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>24,711,922</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>28,297,509</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>21,716,061</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>28,950,000</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>137,583,388</t>
         </is>
       </c>
-      <c r="I19" s="7" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>135,719,131</t>
         </is>
       </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="J22" s="6" t="inlineStr">
         <is>
           <t>137,788,479</t>
         </is>
       </c>
-      <c r="K19" s="7" t="inlineStr">
+      <c r="K22" s="6" t="inlineStr">
         <is>
           <t>149,290,000</t>
         </is>
       </c>
-      <c r="L19" s="7" t="inlineStr">
+      <c r="L22" s="6" t="inlineStr">
         <is>
           <t>92.2</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="14" customHeight="1">
-      <c r="A20" s="8" t="n"/>
-      <c r="B20" s="9" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>粗利額</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>8,189,354</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>9,605,376</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>7,762,409</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>10,518,850</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>73.7</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>44,490,995</t>
         </is>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>44,240,901</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>48,856,582</t>
         </is>
       </c>
-      <c r="K20" s="11" t="inlineStr">
+      <c r="K23" s="7" t="inlineStr">
         <is>
           <t>54,242,270</t>
         </is>
       </c>
-      <c r="L20" s="11" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>90.0</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="14" customHeight="1">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="9" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>粗利%</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>33.1</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>33.9</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>35.7</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>32.3</t>
         </is>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>32.5</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J24" s="7" t="inlineStr">
         <is>
           <t>35.4</t>
         </is>
       </c>
-      <c r="K21" s="11" t="inlineStr">
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="L21" s="11" t="n"/>
-    </row>
-    <row r="22" ht="14" customHeight="1">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="L24" s="7" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>在庫額</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>47,503,782</t>
         </is>
       </c>
-      <c r="D22" s="15" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>32,568,385</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>31,850,741</t>
         </is>
       </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="15" t="inlineStr">
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>47,503,782</t>
         </is>
       </c>
-      <c r="I22" s="15" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>32,568,385</t>
         </is>
       </c>
-      <c r="J22" s="15" t="inlineStr">
+      <c r="J25" s="7" t="inlineStr">
         <is>
           <t>31,850,741</t>
         </is>
       </c>
-      <c r="K22" s="15" t="inlineStr">
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="L22" s="15" t="n"/>
-    </row>
-    <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="L25" s="7" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>9月</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>売上額</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>17,325,492</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>23,476,600</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>21,868,164</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>22,290,000</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>98.1</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>154,908,880</t>
         </is>
       </c>
-      <c r="I23" s="7" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>159,195,731</t>
         </is>
       </c>
-      <c r="J23" s="7" t="inlineStr">
+      <c r="J26" s="6" t="inlineStr">
         <is>
           <t>159,656,643</t>
         </is>
       </c>
-      <c r="K23" s="7" t="inlineStr">
+      <c r="K26" s="6" t="inlineStr">
         <is>
           <t>171,580,000</t>
         </is>
       </c>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="L26" s="6" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="14" customHeight="1">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="9" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>粗利額</t>
         </is>
       </c>
-      <c r="C24" s="10" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>5,348,809</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>8,212,363</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>8,439,703</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>8,101,270</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>104.1</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>49,839,804</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>52,453,264</t>
         </is>
       </c>
-      <c r="J24" s="11" t="inlineStr">
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>57,296,285</t>
         </is>
       </c>
-      <c r="K24" s="11" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
         <is>
           <t>62,343,540</t>
         </is>
       </c>
-      <c r="L24" s="11" t="inlineStr">
+      <c r="L27" s="7" t="inlineStr">
         <is>
           <t>91.9</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="8" t="n"/>
-      <c r="B25" s="9" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>粗利%</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>30.9</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>35.0</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>38.6</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>32.1</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>32.9</t>
         </is>
       </c>
-      <c r="J25" s="11" t="inlineStr">
+      <c r="J28" s="7" t="inlineStr">
         <is>
           <t>35.8</t>
         </is>
       </c>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="K28" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="L25" s="11" t="n"/>
-    </row>
-    <row r="26" ht="14" customHeight="1">
-      <c r="A26" s="12" t="n"/>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="L28" s="7" t="n"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>在庫額</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>46,773,937</t>
         </is>
       </c>
-      <c r="D26" s="15" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>29,355,034</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>27,857,063</t>
         </is>
       </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="G26" s="15" t="n"/>
-      <c r="H26" s="15" t="inlineStr">
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>46,773,937</t>
         </is>
       </c>
-      <c r="I26" s="15" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>29,355,034</t>
         </is>
       </c>
-      <c r="J26" s="15" t="inlineStr">
+      <c r="J29" s="7" t="inlineStr">
         <is>
           <t>27,857,063</t>
         </is>
       </c>
-      <c r="K26" s="15" t="inlineStr">
+      <c r="K29" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="L26" s="15" t="n"/>
-    </row>
-    <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>上半期
-合計</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="L29" s="7" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>上半期</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>売上額</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>154,908,880</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>159,195,731</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>159,656,643</t>
         </is>
       </c>
-      <c r="F27" s="7" t="inlineStr">
+      <c r="F30" s="8" t="inlineStr">
         <is>
           <t>171,580,000</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>154,908,880</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>159,195,731</t>
         </is>
       </c>
-      <c r="J27" s="7" t="inlineStr">
+      <c r="J30" s="8" t="inlineStr">
         <is>
           <t>159,656,643</t>
         </is>
       </c>
-      <c r="K27" s="7" t="inlineStr">
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>171,580,000</t>
         </is>
       </c>
-      <c r="L27" s="7" t="inlineStr">
+      <c r="L30" s="8" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="14" customHeight="1">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="9" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>合　計</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>粗利額</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>49,839,804</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>52,453,264</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>57,296,285</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
         <is>
           <t>62,343,540</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>91.9</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H31" s="8" t="inlineStr">
         <is>
           <t>49,839,804</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>52,453,264</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>57,296,285</t>
         </is>
       </c>
-      <c r="K28" s="11" t="inlineStr">
+      <c r="K31" s="8" t="inlineStr">
         <is>
           <t>62,343,540</t>
         </is>
       </c>
-      <c r="L28" s="11" t="inlineStr">
+      <c r="L31" s="8" t="inlineStr">
         <is>
           <t>91.9</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="14" customHeight="1">
-      <c r="A29" s="8" t="n"/>
-      <c r="B29" s="9" t="inlineStr">
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>粗利%</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>32.1</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>32.9</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>35.8</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>32.1</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>32.9</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>35.8</t>
         </is>
       </c>
-      <c r="K29" s="11" t="inlineStr">
+      <c r="K32" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="L29" s="11" t="n"/>
-    </row>
-    <row r="30" ht="14" customHeight="1">
-      <c r="A30" s="12" t="n"/>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="L32" s="7" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>在庫額</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>46,773,937</t>
         </is>
       </c>
-      <c r="D30" s="15" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>29,355,034</t>
         </is>
       </c>
-      <c r="E30" s="15" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>27,857,063</t>
         </is>
       </c>
-      <c r="F30" s="15" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="15" t="inlineStr">
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>46,773,937</t>
         </is>
       </c>
-      <c r="I30" s="15" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>29,355,034</t>
         </is>
       </c>
-      <c r="J30" s="15" t="inlineStr">
+      <c r="J33" s="7" t="inlineStr">
         <is>
           <t>27,857,063</t>
         </is>
       </c>
-      <c r="K30" s="15" t="inlineStr">
+      <c r="K33" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="L30" s="15" t="n"/>
-    </row>
-    <row r="31" ht="14" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="L33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>売上額</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>16,087,635</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>27,698,307</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>22,114,309</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>23,920,000</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>92.4</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="H34" s="6" t="inlineStr">
         <is>
           <t>170,996,515</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>186,894,038</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr">
+      <c r="J34" s="6" t="inlineStr">
         <is>
           <t>181,770,952</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr">
+      <c r="K34" s="6" t="inlineStr">
         <is>
           <t>195,500,000</t>
         </is>
       </c>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L34" s="6" t="inlineStr">
         <is>
           <t>92.9</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="14" customHeight="1">
-      <c r="A32" s="8" t="n"/>
-      <c r="B32" s="9" t="inlineStr">
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>粗利額</t>
         </is>
       </c>
-      <c r="C32" s="10" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>5,219,810</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>9,665,198</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>8,603,319</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>8,692,960</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G35" s="7" t="inlineStr">
         <is>
           <t>98.9</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>55,059,614</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>62,118,462</t>
         </is>
       </c>
-      <c r="J32" s="11" t="inlineStr">
+      <c r="J35" s="7" t="inlineStr">
         <is>
           <t>65,899,604</t>
         </is>
       </c>
-      <c r="K32" s="11" t="inlineStr">
+      <c r="K35" s="7" t="inlineStr">
         <is>
           <t>71,036,500</t>
         </is>
       </c>
-      <c r="L32" s="11" t="inlineStr">
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>92.7</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="14" customHeight="1">
-      <c r="A33" s="8" t="n"/>
-      <c r="B33" s="9" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>粗利%</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>32.4</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>34.9</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>38.9</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>32.1</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>33.2</t>
         </is>
       </c>
-      <c r="J33" s="11" t="inlineStr">
+      <c r="J36" s="7" t="inlineStr">
         <is>
           <t>36.2</t>
         </is>
       </c>
-      <c r="K33" s="11" t="inlineStr">
+      <c r="K36" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="L33" s="11" t="n"/>
-    </row>
-    <row r="34" ht="14" customHeight="1">
-      <c r="A34" s="12" t="n"/>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="L36" s="7" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>在庫額</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>41,005,284</t>
         </is>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>28,396,479</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>30,466,816</t>
         </is>
       </c>
-      <c r="F34" s="15" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="G34" s="15" t="n"/>
-      <c r="H34" s="15" t="inlineStr">
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>41,005,284</t>
         </is>
       </c>
-      <c r="I34" s="15" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>28,396,479</t>
         </is>
       </c>
-      <c r="J34" s="15" t="inlineStr">
+      <c r="J37" s="7" t="inlineStr">
         <is>
           <t>30,466,816</t>
         </is>
       </c>
-      <c r="K34" s="15" t="inlineStr">
+      <c r="K37" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="L34" s="15" t="n"/>
-    </row>
-    <row r="35" ht="14" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="L37" s="7" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>11月</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>売上額</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>17,319,499</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>27,255,830</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>23,854,112</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>24,350,000</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>97.9</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="H38" s="6" t="inlineStr">
         <is>
           <t>188,316,014</t>
         </is>
       </c>
-      <c r="I35" s="7" t="inlineStr">
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>214,149,868</t>
         </is>
       </c>
-      <c r="J35" s="7" t="inlineStr">
+      <c r="J38" s="6" t="inlineStr">
         <is>
           <t>205,625,064</t>
         </is>
       </c>
-      <c r="K35" s="7" t="inlineStr">
+      <c r="K38" s="6" t="inlineStr">
         <is>
           <t>219,850,000</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="L38" s="6" t="inlineStr">
         <is>
           <t>93.5</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="14" customHeight="1">
-      <c r="A36" s="8" t="n"/>
-      <c r="B36" s="9" t="inlineStr">
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>粗利額</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>6,265,993</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>9,318,522</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>8,425,104</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>8,849,050</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>95.2</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>61,325,607</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>71,436,990</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr">
         <is>
           <t>74,324,708</t>
         </is>
       </c>
-      <c r="K36" s="11" t="inlineStr">
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>79,885,550</t>
         </is>
       </c>
-      <c r="L36" s="11" t="inlineStr">
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>93.0</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="14" customHeight="1">
-      <c r="A37" s="8" t="n"/>
-      <c r="B37" s="9" t="inlineStr">
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>粗利%</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>36.2</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>34.2</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>35.3</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="G40" s="7" t="n"/>
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>32.5</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>33.3</t>
         </is>
       </c>
-      <c r="J37" s="11" t="inlineStr">
+      <c r="J40" s="7" t="inlineStr">
         <is>
           <t>36.1</t>
         </is>
       </c>
-      <c r="K37" s="11" t="inlineStr">
+      <c r="K40" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="L37" s="11" t="n"/>
-    </row>
-    <row r="38" ht="14" customHeight="1">
-      <c r="A38" s="12" t="n"/>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="L40" s="7" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>在庫額</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>39,810,796</t>
         </is>
       </c>
-      <c r="D38" s="15" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>28,175,606</t>
         </is>
       </c>
-      <c r="E38" s="15" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>30,273,422</t>
         </is>
       </c>
-      <c r="F38" s="15" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="G38" s="15" t="n"/>
-      <c r="H38" s="15" t="inlineStr">
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>39,810,796</t>
         </is>
       </c>
-      <c r="I38" s="15" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>28,175,606</t>
         </is>
       </c>
-      <c r="J38" s="15" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>30,273,422</t>
         </is>
       </c>
-      <c r="K38" s="15" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="L38" s="15" t="n"/>
-    </row>
-    <row r="39" ht="14" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="L41" s="7" t="n"/>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>12月</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>売上額</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>29,702,144</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>39,450,417</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>31,929,465</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <t>37,770,000</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>84.5</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="H42" s="6" t="inlineStr">
         <is>
           <t>218,018,158</t>
         </is>
       </c>
-      <c r="I39" s="7" t="inlineStr">
+      <c r="I42" s="6" t="inlineStr">
         <is>
           <t>253,600,285</t>
         </is>
       </c>
-      <c r="J39" s="7" t="inlineStr">
+      <c r="J42" s="6" t="inlineStr">
         <is>
           <t>237,554,529</t>
         </is>
       </c>
-      <c r="K39" s="7" t="inlineStr">
+      <c r="K42" s="6" t="inlineStr">
         <is>
           <t>257,620,000</t>
         </is>
       </c>
-      <c r="L39" s="7" t="inlineStr">
+      <c r="L42" s="6" t="inlineStr">
         <is>
           <t>92.2</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="14" customHeight="1">
-      <c r="A40" s="8" t="n"/>
-      <c r="B40" s="9" t="inlineStr">
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="7" t="n"/>
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>粗利額</t>
         </is>
       </c>
-      <c r="C40" s="10" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>9,592,434</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>13,675,891</t>
         </is>
       </c>
-      <c r="E40" s="11" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>11,417,498</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>13,710,510</t>
         </is>
       </c>
-      <c r="G40" s="11" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr">
         <is>
           <t>83.2</t>
         </is>
       </c>
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>70,918,041</t>
         </is>
       </c>
-      <c r="I40" s="11" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>85,112,881</t>
         </is>
       </c>
-      <c r="J40" s="11" t="inlineStr">
+      <c r="J43" s="7" t="inlineStr">
         <is>
           <t>85,742,206</t>
         </is>
       </c>
-      <c r="K40" s="11" t="inlineStr">
+      <c r="K43" s="7" t="inlineStr">
         <is>
           <t>93,596,060</t>
         </is>
       </c>
-      <c r="L40" s="11" t="inlineStr">
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>91.6</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="14" customHeight="1">
-      <c r="A41" s="8" t="n"/>
-      <c r="B41" s="9" t="inlineStr">
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="7" t="n"/>
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>粗利%</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>32.3</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>34.7</t>
         </is>
       </c>
-      <c r="E41" s="11" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>35.8</t>
         </is>
       </c>
-      <c r="F41" s="11" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>32.5</t>
         </is>
       </c>
-      <c r="I41" s="11" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>33.5</t>
         </is>
       </c>
-      <c r="J41" s="11" t="inlineStr">
+      <c r="J44" s="7" t="inlineStr">
         <is>
           <t>36.0</t>
         </is>
       </c>
-      <c r="K41" s="11" t="inlineStr">
+      <c r="K44" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="L41" s="11" t="n"/>
-    </row>
-    <row r="42" ht="14" customHeight="1">
-      <c r="A42" s="12" t="n"/>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="L44" s="7" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="7" t="n"/>
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>在庫額</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>39,484,748</t>
         </is>
       </c>
-      <c r="D42" s="15" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>29,037,575</t>
         </is>
       </c>
-      <c r="E42" s="15" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>30,780,171</t>
         </is>
       </c>
-      <c r="F42" s="15" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="G42" s="15" t="n"/>
-      <c r="H42" s="15" t="inlineStr">
+      <c r="G45" s="7" t="n"/>
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>39,484,748</t>
         </is>
       </c>
-      <c r="I42" s="15" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>29,037,575</t>
         </is>
       </c>
-      <c r="J42" s="15" t="inlineStr">
+      <c r="J45" s="7" t="inlineStr">
         <is>
           <t>30,780,171</t>
         </is>
       </c>
-      <c r="K42" s="15" t="inlineStr">
+      <c r="K45" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="L42" s="15" t="n"/>
-    </row>
-    <row r="43" ht="14" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="L45" s="7" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>1月</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>売上額</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>23,843,539</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>29,087,448</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>33,071,695</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>28,910,000</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>114.3</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>241,861,697</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="I46" s="6" t="inlineStr">
         <is>
           <t>282,687,733</t>
         </is>
       </c>
-      <c r="J43" s="7" t="inlineStr">
+      <c r="J46" s="6" t="inlineStr">
         <is>
           <t>270,626,224</t>
         </is>
       </c>
-      <c r="K43" s="7" t="inlineStr">
+      <c r="K46" s="6" t="inlineStr">
         <is>
           <t>286,530,000</t>
         </is>
       </c>
-      <c r="L43" s="7" t="inlineStr">
+      <c r="L46" s="6" t="inlineStr">
         <is>
           <t>94.4</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="8" t="n"/>
-      <c r="B44" s="9" t="inlineStr">
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>粗利額</t>
         </is>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>7,753,370</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>10,209,939</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>11,217,186</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>10,494,330</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr">
+      <c r="G47" s="7" t="inlineStr">
         <is>
           <t>106.8</t>
         </is>
       </c>
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>78,671,411</t>
         </is>
       </c>
-      <c r="I44" s="11" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>95,322,820</t>
         </is>
       </c>
-      <c r="J44" s="11" t="inlineStr">
+      <c r="J47" s="7" t="inlineStr">
         <is>
           <t>96,959,392</t>
         </is>
       </c>
-      <c r="K44" s="11" t="inlineStr">
+      <c r="K47" s="7" t="inlineStr">
         <is>
           <t>104,090,390</t>
         </is>
       </c>
-      <c r="L44" s="11" t="inlineStr">
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>93.1</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="14" customHeight="1">
-      <c r="A45" s="8" t="n"/>
-      <c r="B45" s="9" t="inlineStr">
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="7" t="n"/>
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>粗利%</t>
         </is>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>32.5</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>35.1</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>33.9</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="G45" s="11" t="n"/>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="G48" s="7" t="n"/>
+      <c r="H48" s="7" t="inlineStr">
         <is>
           <t>32.5</t>
         </is>
       </c>
-      <c r="I45" s="11" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>33.7</t>
         </is>
       </c>
-      <c r="J45" s="11" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
         <is>
           <t>35.8</t>
         </is>
       </c>
-      <c r="K45" s="11" t="inlineStr">
+      <c r="K48" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="L45" s="11" t="n"/>
-    </row>
-    <row r="46" ht="14" customHeight="1">
-      <c r="A46" s="12" t="n"/>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="L48" s="7" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="7" t="n"/>
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>在庫額</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>37,621,437</t>
         </is>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>29,134,761</t>
         </is>
       </c>
-      <c r="E46" s="15" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>30,783,818</t>
         </is>
       </c>
-      <c r="F46" s="15" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="G46" s="15" t="n"/>
-      <c r="H46" s="15" t="inlineStr">
+      <c r="G49" s="7" t="n"/>
+      <c r="H49" s="7" t="inlineStr">
         <is>
           <t>37,621,437</t>
         </is>
       </c>
-      <c r="I46" s="15" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>29,134,761</t>
         </is>
       </c>
-      <c r="J46" s="15" t="inlineStr">
+      <c r="J49" s="7" t="inlineStr">
         <is>
           <t>30,783,818</t>
         </is>
       </c>
-      <c r="K46" s="15" t="inlineStr">
+      <c r="K49" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="L46" s="15" t="n"/>
-    </row>
-    <row r="47" ht="14" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="L49" s="7" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>2月</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>売上額</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>19,026,373</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>26,304,446</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>17,024,012</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <t>24,750,000</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G50" s="6" t="inlineStr">
         <is>
           <t>68.7</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="H50" s="6" t="inlineStr">
         <is>
           <t>260,888,070</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>308,992,179</t>
         </is>
       </c>
-      <c r="J47" s="7" t="inlineStr">
+      <c r="J50" s="6" t="inlineStr">
         <is>
           <t>287,650,236</t>
         </is>
       </c>
-      <c r="K47" s="7" t="inlineStr">
+      <c r="K50" s="6" t="inlineStr">
         <is>
           <t>311,280,000</t>
         </is>
       </c>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="L50" s="6" t="inlineStr">
         <is>
           <t>92.4</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="14" customHeight="1">
-      <c r="A48" s="8" t="n"/>
-      <c r="B48" s="9" t="inlineStr">
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="7" t="n"/>
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>粗利額</t>
         </is>
       </c>
-      <c r="C48" s="10" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>6,649,269</t>
         </is>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>8,750,616</t>
         </is>
       </c>
-      <c r="E48" s="11" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>6,008,094</t>
         </is>
       </c>
-      <c r="F48" s="11" t="inlineStr">
-        <is>
-          <t>9,984,250</t>
-        </is>
-      </c>
-      <c r="G48" s="11" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>8,984,250</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>66.8</t>
         </is>
       </c>
-      <c r="H48" s="11" t="inlineStr">
+      <c r="H51" s="7" t="inlineStr">
         <is>
           <t>85,320,680</t>
         </is>
       </c>
-      <c r="I48" s="11" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>104,073,436</t>
         </is>
       </c>
-      <c r="J48" s="11" t="inlineStr">
+      <c r="J51" s="7" t="inlineStr">
         <is>
           <t>102,967,486</t>
         </is>
       </c>
-      <c r="K48" s="11" t="inlineStr">
+      <c r="K51" s="7" t="inlineStr">
         <is>
           <t>113,074,640</t>
         </is>
       </c>
-      <c r="L48" s="11" t="inlineStr">
+      <c r="L51" s="7" t="inlineStr">
         <is>
           <t>91.0</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="14" customHeight="1">
-      <c r="A49" s="8" t="n"/>
-      <c r="B49" s="9" t="inlineStr">
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="7" t="n"/>
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>粗利%</t>
         </is>
       </c>
-      <c r="C49" s="10" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>34.9</t>
         </is>
       </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>33.3</t>
         </is>
       </c>
-      <c r="E49" s="11" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>35.3</t>
         </is>
       </c>
-      <c r="F49" s="11" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="G49" s="11" t="n"/>
-      <c r="H49" s="11" t="inlineStr">
+      <c r="G52" s="7" t="n"/>
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>32.7</t>
         </is>
       </c>
-      <c r="I49" s="11" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>33.6</t>
         </is>
       </c>
-      <c r="J49" s="11" t="inlineStr">
+      <c r="J52" s="7" t="inlineStr">
         <is>
           <t>35.7</t>
         </is>
       </c>
-      <c r="K49" s="11" t="inlineStr">
+      <c r="K52" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="L49" s="11" t="n"/>
-    </row>
-    <row r="50" ht="14" customHeight="1">
-      <c r="A50" s="12" t="n"/>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="L52" s="7" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="7" t="n"/>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>在庫額</t>
         </is>
       </c>
-      <c r="C50" s="14" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>34,668,284</t>
         </is>
       </c>
-      <c r="D50" s="15" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>30,898,451</t>
         </is>
       </c>
-      <c r="E50" s="15" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>31,270,029</t>
         </is>
       </c>
-      <c r="F50" s="15" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="G50" s="15" t="n"/>
-      <c r="H50" s="15" t="inlineStr">
+      <c r="G53" s="7" t="n"/>
+      <c r="H53" s="7" t="inlineStr">
         <is>
           <t>34,668,284</t>
         </is>
       </c>
-      <c r="I50" s="15" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>30,898,451</t>
         </is>
       </c>
-      <c r="J50" s="15" t="inlineStr">
+      <c r="J53" s="7" t="inlineStr">
         <is>
           <t>31,270,029</t>
         </is>
       </c>
-      <c r="K50" s="15" t="inlineStr">
+      <c r="K53" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="L50" s="15" t="n"/>
-    </row>
-    <row r="51" ht="14" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="L53" s="7" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
         <is>
           <t>3月</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>売上額</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>21,830,080</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>30,761,702</t>
         </is>
       </c>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <t>28,720,000</t>
         </is>
       </c>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="G54" s="6" t="n"/>
+      <c r="H54" s="6" t="inlineStr">
         <is>
           <t>282,718,150</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="I54" s="6" t="inlineStr">
         <is>
           <t>339,753,881</t>
         </is>
       </c>
-      <c r="J51" s="7" t="n"/>
-      <c r="K51" s="7" t="inlineStr">
+      <c r="J54" s="6" t="n"/>
+      <c r="K54" s="6" t="inlineStr">
         <is>
           <t>340,000,000</t>
         </is>
       </c>
-      <c r="L51" s="7" t="n"/>
-    </row>
-    <row r="52" ht="14" customHeight="1">
-      <c r="A52" s="8" t="n"/>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="L54" s="6" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="7" t="n"/>
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>粗利額</t>
         </is>
       </c>
-      <c r="C52" s="10" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>7,433,681</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>11,169,182</t>
         </is>
       </c>
-      <c r="E52" s="11" t="n"/>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="E55" s="7" t="n"/>
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>10,425,360</t>
         </is>
       </c>
-      <c r="G52" s="11" t="n"/>
-      <c r="H52" s="11" t="inlineStr">
+      <c r="G55" s="7" t="n"/>
+      <c r="H55" s="7" t="inlineStr">
         <is>
           <t>92,754,361</t>
         </is>
       </c>
-      <c r="I52" s="11" t="inlineStr">
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>115,242,618</t>
         </is>
       </c>
-      <c r="J52" s="11" t="n"/>
-      <c r="K52" s="11" t="inlineStr">
+      <c r="J55" s="7" t="n"/>
+      <c r="K55" s="7" t="inlineStr">
         <is>
           <t>123,500,000</t>
         </is>
       </c>
-      <c r="L52" s="11" t="n"/>
-    </row>
-    <row r="53" ht="14" customHeight="1">
-      <c r="A53" s="8" t="n"/>
-      <c r="B53" s="9" t="inlineStr">
+      <c r="L55" s="7" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="7" t="n"/>
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>粗利%</t>
         </is>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>34.1</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="E53" s="11" t="n"/>
-      <c r="F53" s="11" t="inlineStr">
+      <c r="E56" s="7" t="n"/>
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="G53" s="11" t="n"/>
-      <c r="H53" s="11" t="inlineStr">
+      <c r="G56" s="7" t="n"/>
+      <c r="H56" s="7" t="inlineStr">
         <is>
           <t>32.8</t>
         </is>
       </c>
-      <c r="I53" s="11" t="inlineStr">
+      <c r="I56" s="7" t="inlineStr">
         <is>
           <t>33.9</t>
         </is>
       </c>
-      <c r="J53" s="11" t="n"/>
-      <c r="K53" s="11" t="inlineStr">
+      <c r="J56" s="7" t="n"/>
+      <c r="K56" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="L53" s="11" t="n"/>
-    </row>
-    <row r="54" ht="14" customHeight="1">
-      <c r="A54" s="12" t="n"/>
-      <c r="B54" s="13" t="inlineStr">
+      <c r="L56" s="7" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="7" t="n"/>
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>在庫額</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>30,329,880</t>
         </is>
       </c>
-      <c r="D54" s="15" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>27,410,622</t>
         </is>
       </c>
-      <c r="E54" s="15" t="n"/>
-      <c r="F54" s="15" t="inlineStr">
+      <c r="E57" s="7" t="n"/>
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="G54" s="15" t="n"/>
-      <c r="H54" s="15" t="inlineStr">
+      <c r="G57" s="7" t="n"/>
+      <c r="H57" s="7" t="inlineStr">
         <is>
           <t>30,329,880</t>
         </is>
       </c>
-      <c r="I54" s="15" t="inlineStr">
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t>27,410,622</t>
         </is>
       </c>
-      <c r="J54" s="15" t="n"/>
-      <c r="K54" s="15" t="inlineStr">
+      <c r="J57" s="7" t="n"/>
+      <c r="K57" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="L54" s="15" t="n"/>
-    </row>
-    <row r="55" ht="14" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>下半期
-合計</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="L57" s="7" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>下半期</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>売上額</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>127,809,270</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>180,558,150</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>127,993,593</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>168,420,000</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>75.9</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
+      <c r="H58" s="8" t="inlineStr">
         <is>
           <t>127,809,270</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="I58" s="8" t="inlineStr">
         <is>
           <t>180,558,150</t>
         </is>
       </c>
-      <c r="J55" s="7" t="inlineStr">
+      <c r="J58" s="8" t="inlineStr">
         <is>
           <t>127,993,593</t>
         </is>
       </c>
-      <c r="K55" s="7" t="inlineStr">
+      <c r="K58" s="8" t="inlineStr">
         <is>
           <t>168,420,000</t>
         </is>
       </c>
-      <c r="L55" s="7" t="inlineStr">
+      <c r="L58" s="8" t="inlineStr">
         <is>
           <t>75.9</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="14" customHeight="1">
-      <c r="A56" s="8" t="n"/>
-      <c r="B56" s="9" t="inlineStr">
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>合　計</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>粗利額</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>42,914,557</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>62,789,354</t>
         </is>
       </c>
-      <c r="E56" s="11" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>45,671,201</t>
         </is>
       </c>
-      <c r="F56" s="11" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>61,156,460</t>
         </is>
       </c>
-      <c r="G56" s="11" t="inlineStr">
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>74.6</t>
         </is>
       </c>
-      <c r="H56" s="11" t="inlineStr">
+      <c r="H59" s="8" t="inlineStr">
         <is>
           <t>42,914,557</t>
         </is>
       </c>
-      <c r="I56" s="11" t="inlineStr">
+      <c r="I59" s="8" t="inlineStr">
         <is>
           <t>62,789,354</t>
         </is>
       </c>
-      <c r="J56" s="11" t="inlineStr">
+      <c r="J59" s="8" t="inlineStr">
         <is>
           <t>45,671,201</t>
         </is>
       </c>
-      <c r="K56" s="11" t="inlineStr">
+      <c r="K59" s="8" t="inlineStr">
         <is>
           <t>61,156,460</t>
         </is>
       </c>
-      <c r="L56" s="11" t="inlineStr">
+      <c r="L59" s="8" t="inlineStr">
         <is>
           <t>74.6</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="14" customHeight="1">
-      <c r="A57" s="8" t="n"/>
-      <c r="B57" s="9" t="inlineStr">
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="7" t="n"/>
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>粗利%</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>33.5</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>34.7</t>
         </is>
       </c>
-      <c r="E57" s="11" t="inlineStr">
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>35.6</t>
         </is>
       </c>
-      <c r="F57" s="11" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="G57" s="11" t="n"/>
-      <c r="H57" s="11" t="inlineStr">
+      <c r="G60" s="7" t="n"/>
+      <c r="H60" s="7" t="inlineStr">
         <is>
           <t>33.5</t>
         </is>
       </c>
-      <c r="I57" s="11" t="inlineStr">
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t>34.7</t>
         </is>
       </c>
-      <c r="J57" s="11" t="inlineStr">
+      <c r="J60" s="7" t="inlineStr">
         <is>
           <t>35.6</t>
         </is>
       </c>
-      <c r="K57" s="11" t="inlineStr">
+      <c r="K60" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="L57" s="11" t="n"/>
-    </row>
-    <row r="58" ht="14" customHeight="1">
-      <c r="A58" s="12" t="n"/>
-      <c r="B58" s="13" t="inlineStr">
+      <c r="L60" s="7" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="7" t="n"/>
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>在庫額</t>
         </is>
       </c>
-      <c r="C58" s="14" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>30,329,880</t>
         </is>
       </c>
-      <c r="D58" s="15" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>27,410,622</t>
         </is>
       </c>
-      <c r="E58" s="15" t="inlineStr">
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>31,270,029</t>
         </is>
       </c>
-      <c r="F58" s="15" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="G58" s="15" t="n"/>
-      <c r="H58" s="15" t="inlineStr">
+      <c r="G61" s="7" t="n"/>
+      <c r="H61" s="7" t="inlineStr">
         <is>
           <t>30,329,880</t>
         </is>
       </c>
-      <c r="I58" s="15" t="inlineStr">
+      <c r="I61" s="7" t="inlineStr">
         <is>
           <t>27,410,622</t>
         </is>
       </c>
-      <c r="J58" s="15" t="inlineStr">
+      <c r="J61" s="7" t="inlineStr">
         <is>
           <t>31,270,029</t>
         </is>
       </c>
-      <c r="K58" s="15" t="inlineStr">
+      <c r="K61" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="L58" s="15" t="n"/>
-    </row>
-    <row r="59" ht="14" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>年間
-合計</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="L61" s="7" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>年　間</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>売上額</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>282,718,150</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>339,753,881</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>287,650,236</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>340,000,000</t>
         </is>
       </c>
-      <c r="G59" s="7" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>84.6</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>282,718,150</t>
         </is>
       </c>
-      <c r="I59" s="7" t="inlineStr">
+      <c r="I62" s="8" t="inlineStr">
         <is>
           <t>339,753,881</t>
         </is>
       </c>
-      <c r="J59" s="7" t="inlineStr">
+      <c r="J62" s="8" t="inlineStr">
         <is>
           <t>287,650,236</t>
         </is>
       </c>
-      <c r="K59" s="7" t="inlineStr">
+      <c r="K62" s="8" t="inlineStr">
         <is>
           <t>340,000,000</t>
         </is>
       </c>
-      <c r="L59" s="7" t="inlineStr">
+      <c r="L62" s="8" t="inlineStr">
         <is>
           <t>84.6</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="14" customHeight="1">
-      <c r="A60" s="8" t="n"/>
-      <c r="B60" s="9" t="inlineStr">
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>合　計</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>粗利額</t>
         </is>
       </c>
-      <c r="C60" s="10" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>92,754,361</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>115,242,618</t>
         </is>
       </c>
-      <c r="E60" s="11" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>102,967,486</t>
         </is>
       </c>
-      <c r="F60" s="11" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>123,500,000</t>
         </is>
       </c>
-      <c r="G60" s="11" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>83.3</t>
         </is>
       </c>
-      <c r="H60" s="11" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr">
         <is>
           <t>92,754,361</t>
         </is>
       </c>
-      <c r="I60" s="11" t="inlineStr">
+      <c r="I63" s="8" t="inlineStr">
         <is>
           <t>115,242,618</t>
         </is>
       </c>
-      <c r="J60" s="11" t="inlineStr">
+      <c r="J63" s="8" t="inlineStr">
         <is>
           <t>102,967,486</t>
         </is>
       </c>
-      <c r="K60" s="11" t="inlineStr">
+      <c r="K63" s="8" t="inlineStr">
         <is>
           <t>123,500,000</t>
         </is>
       </c>
-      <c r="L60" s="11" t="inlineStr">
+      <c r="L63" s="8" t="inlineStr">
         <is>
           <t>83.3</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="14" customHeight="1">
-      <c r="A61" s="8" t="n"/>
-      <c r="B61" s="9" t="inlineStr">
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="7" t="n"/>
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>粗利%</t>
         </is>
       </c>
-      <c r="C61" s="10" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>32.8</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>33.9</t>
         </is>
       </c>
-      <c r="E61" s="11" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>35.7</t>
         </is>
       </c>
-      <c r="F61" s="11" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="G61" s="11" t="n"/>
-      <c r="H61" s="11" t="inlineStr">
+      <c r="G64" s="7" t="n"/>
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>32.8</t>
         </is>
       </c>
-      <c r="I61" s="11" t="inlineStr">
+      <c r="I64" s="7" t="inlineStr">
         <is>
           <t>33.9</t>
         </is>
       </c>
-      <c r="J61" s="11" t="inlineStr">
+      <c r="J64" s="7" t="inlineStr">
         <is>
           <t>35.7</t>
         </is>
       </c>
-      <c r="K61" s="11" t="inlineStr">
+      <c r="K64" s="7" t="inlineStr">
         <is>
           <t>36.3</t>
         </is>
       </c>
-      <c r="L61" s="11" t="n"/>
-    </row>
-    <row r="62" ht="14" customHeight="1">
-      <c r="A62" s="12" t="n"/>
-      <c r="B62" s="13" t="inlineStr">
+      <c r="L64" s="7" t="n"/>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="7" t="n"/>
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>在庫額</t>
         </is>
       </c>
-      <c r="C62" s="14" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>30,329,880</t>
         </is>
       </c>
-      <c r="D62" s="15" t="inlineStr">
+      <c r="D65" s="7" t="inlineStr">
         <is>
           <t>27,410,622</t>
         </is>
       </c>
-      <c r="E62" s="15" t="inlineStr">
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>31,270,029</t>
         </is>
       </c>
-      <c r="F62" s="15" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="G62" s="15" t="n"/>
-      <c r="H62" s="15" t="inlineStr">
+      <c r="G65" s="7" t="n"/>
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>30,329,880</t>
         </is>
       </c>
-      <c r="I62" s="15" t="inlineStr">
+      <c r="I65" s="7" t="inlineStr">
         <is>
           <t>27,410,622</t>
         </is>
       </c>
-      <c r="J62" s="15" t="inlineStr">
+      <c r="J65" s="7" t="inlineStr">
         <is>
           <t>31,270,029</t>
         </is>
       </c>
-      <c r="K62" s="15" t="inlineStr">
+      <c r="K65" s="7" t="inlineStr">
         <is>
           <t>28,000,000</t>
         </is>
       </c>
-      <c r="L62" s="15" t="n"/>
+      <c r="L65" s="7" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A47:A50"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A31:A34"/>
-    <mergeCell ref="A43:A46"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A3:A6"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A51:A54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
